--- a/density_data.xlsx
+++ b/density_data.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-18 09:18:12</t>
+          <t>2026-01-06 15:25:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,22 +511,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.329</v>
+        <v>1.231</v>
       </c>
       <c r="G2" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H2" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I2" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J2" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3274</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="3">
@@ -537,7 +537,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-12-18 09:18:35</t>
+          <t>2026-01-06 15:25:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -556,22 +556,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G3" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H3" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I3" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J3" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K3" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-12-18 09:18:52</t>
+          <t>2026-01-06 15:26:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G4" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H4" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I4" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J4" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K4" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="5">
@@ -627,7 +627,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-12-18 09:19:09</t>
+          <t>2026-01-06 15:26:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G5" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H5" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I5" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J5" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K5" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="6">
@@ -672,7 +672,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-12-18 09:19:27</t>
+          <t>2026-01-06 15:26:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G6" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H6" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I6" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J6" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K6" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-12-18 09:19:47</t>
+          <t>2026-01-06 15:27:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G7" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H7" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I7" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J7" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K7" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-12-18 09:20:08</t>
+          <t>2026-01-06 15:27:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -771,28 +771,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G8" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H8" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I8" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J8" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K8" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-12-18 09:20:28</t>
+          <t>2026-01-06 15:28:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G9" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H9" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I9" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J9" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K9" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-12-18 09:20:48</t>
+          <t>2026-01-06 15:28:19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -846,28 +846,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G10" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H10" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I10" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J10" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K10" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-12-18 09:21:11</t>
+          <t>2026-01-06 15:28:43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -881,25 +881,30 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="G11" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="H11" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="I11" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="J11" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
       <c r="K11" t="n">
-        <v>1.327</v>
+        <v>1.231</v>
       </c>
     </row>
     <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-01-06 15:30:03</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Model011</t>
@@ -909,6 +914,18 @@
         <is>
           <t>早班</t>
         </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.2977</v>
       </c>
     </row>
     <row r="13">

--- a/density_data.xlsx
+++ b/density_data.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.5546875" bestFit="1" customWidth="1" min="1" max="2"/>
@@ -492,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-06 15:25:34</t>
+          <t>2026-01-26 08:09:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Machine001</t>
+          <t>Machine002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Model001</t>
+          <t>Model002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -511,22 +512,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="G2" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="H2" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="K2" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="3">
@@ -537,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01-06 15:25:54</t>
+          <t>2026-01-26 08:09:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Machine002</t>
+          <t>Machine003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Model002</t>
+          <t>Model003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -556,22 +551,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="G3" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="H3" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="K3" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="4">
@@ -582,17 +571,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-01-06 15:26:15</t>
+          <t>2026-01-26 08:09:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Machine003</t>
+          <t>Machine004</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Model003</t>
+          <t>Model004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -601,22 +590,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="G4" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="H4" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="K4" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="5">
@@ -627,17 +610,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01-06 15:26:39</t>
+          <t>2026-01-26 08:09:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Machine004</t>
+          <t>Machine005</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Model004</t>
+          <t>Model005</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,346 +629,126 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="G5" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="H5" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.231</v>
+        <v>1.111</v>
       </c>
       <c r="K5" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2024-01-15 08:30:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:26:59</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Machine005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Model005</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:27:20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Machine006</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Model006</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:27:41</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Machine007</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Model007</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:28:02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Machine008</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Model008</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:28:19</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Model009</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:28:43</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Model010</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.231</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-01-06 15:30:03</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Model011</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.331</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.331</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.2977</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Model012</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>早班</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2023-09-18 10:00:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2025-12-25 09:15:16</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TestModel</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>白班</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.2345</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.234</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.2342</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.2347</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.2345</v>
+        <v>1.111</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>来样时间</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>测试时间</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>机台号</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>产品型号</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>班次</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>密度1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>密度2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>密度3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>密度4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>密度5</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>平均值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-01-15 08:30:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01-19 09:49:37</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Machine001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Model001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>早班</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.2565</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/density_data.xlsx
+++ b/density_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-26 08:09:47</t>
+          <t>2026-02-05 15:12:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -512,16 +512,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.111</v>
+        <v>1.335</v>
       </c>
       <c r="G2" t="n">
-        <v>1.111</v>
+        <v>1.335</v>
       </c>
       <c r="H2" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.335</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.335</v>
       </c>
       <c r="K2" t="n">
-        <v>1.111</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01-26 08:09:51</t>
+          <t>2026-02-05 15:10:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -551,16 +557,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
       </c>
       <c r="G3" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
       </c>
       <c r="H3" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.335</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.335</v>
       </c>
       <c r="K3" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +583,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-01-26 08:09:54</t>
+          <t>2026-02-05 15:10:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -590,16 +602,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
       </c>
       <c r="G4" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
       </c>
       <c r="K4" t="n">
-        <v>1.111</v>
+        <v>3.335</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +619,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01-26 08:09:56</t>
+          <t>2026-02-05 15:06:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -627,18 +636,6 @@
         <is>
           <t>早班</t>
         </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.111</v>
       </c>
     </row>
   </sheetData>
